--- a/resources/combat/spell_group.xlsx
+++ b/resources/combat/spell_group.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SpellGroup" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpellGroup" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1">SpellGroup!#REF!</definedName>
@@ -894,7 +894,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.71928571428571" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
@@ -1065,6 +1065,21 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>朱雀组</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>900016</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/combat/spell_group.xlsx
+++ b/resources/combat/spell_group.xlsx
@@ -894,7 +894,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.71928571428571" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
@@ -1067,14 +1067,29 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
+        <v>620</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>焚天核心组</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>8600,8601</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
         <v>630</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>朱雀组</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>900016</t>
         </is>

--- a/resources/combat/spell_group.xlsx
+++ b/resources/combat/spell_group.xlsx
@@ -1,19 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\重要文档\RoundCA\data_table\normal\combat\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" activeTab="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" r:id="rId1"/>
-    <sheet name="SpellGroup" sheetId="3" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpellGroup" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">SpellGroup!#REF!</definedName>
@@ -239,184 +233,86 @@
     <definedName name="Z_FAF1ADB8_46A9_40B0_AA1B_9C75E39038F2_.wvu.FilterData" localSheetId="1" hidden="1">SpellGroup!$A$1:$B$4</definedName>
     <definedName name="Z_FF6A625A_6008_4A1D_8FF0_F8A30B9F02A0_.wvu.FilterData" localSheetId="1" hidden="1">SpellGroup!$A$1:$B$4</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
-  <si>
-    <t>表名</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>生成文件</t>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>列作用说明</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>导出目标</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要导出的sheet</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>导出文件</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SERVER</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CLIENT</t>
-  </si>
-  <si>
-    <t>名称</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>name:string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能列表</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>spell_ids:list[int]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>group_id:int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpellGroup</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>combat/spell_group.py</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能组表</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>102,103,104,105,106,107,108,109,110</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>201,202,203,204,205,206,207,208,209</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>301,303,303,304,305,306,307,308,309</t>
-  </si>
-  <si>
-    <t>401,404,403,404,405,406,407,408,409</t>
-  </si>
-  <si>
-    <t>501,505,503,504,505,506,507,508,509</t>
-  </si>
-  <si>
-    <t>601,606,603,604,605,606,607,608,609</t>
-  </si>
-  <si>
-    <t>701,707,703,704,705,706,707,708,709</t>
-  </si>
-  <si>
-    <t>801,808,803,804,805,806,807,808,809</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="9">
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color indexed="8"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color indexed="8"/>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color indexed="8"/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color indexed="8"/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color indexed="8"/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,102 +348,105 @@
     </border>
   </borders>
   <cellStyleXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="9"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="9"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="9" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 11" xfId="11"/>
-    <cellStyle name="常规 2" xfId="4"/>
+    <cellStyle name="常规 6" xfId="1"/>
     <cellStyle name="常规 2 2" xfId="2"/>
     <cellStyle name="常规 2 3" xfId="3"/>
+    <cellStyle name="常规 2" xfId="4"/>
     <cellStyle name="常规 3" xfId="5"/>
     <cellStyle name="常规 4" xfId="6"/>
     <cellStyle name="常规 5" xfId="7"/>
-    <cellStyle name="常规 6" xfId="1"/>
-    <cellStyle name="常规 7" xfId="10"/>
     <cellStyle name="常规_CONFIG" xfId="8"/>
     <cellStyle name="常规_Sheet1" xfId="9"/>
+    <cellStyle name="常规 7" xfId="10"/>
+    <cellStyle name="常规 11" xfId="11"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -582,14 +481,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -850,235 +809,339 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="65" style="8" customWidth="1"/>
-    <col min="3" max="3" width="49.5" style="8" customWidth="1"/>
-    <col min="4" max="4" width="30.125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="23.5" style="8" customWidth="1"/>
-    <col min="6" max="6" width="19.25" style="8" customWidth="1"/>
-    <col min="8" max="8" width="21.375" style="8" customWidth="1"/>
+    <col width="21.125" customWidth="1" style="8" min="1" max="1"/>
+    <col width="65" customWidth="1" style="8" min="2" max="2"/>
+    <col width="49.5" customWidth="1" style="8" min="3" max="3"/>
+    <col width="30.125" customWidth="1" style="8" min="4" max="4"/>
+    <col width="23.5" customWidth="1" style="8" min="5" max="5"/>
+    <col width="19.25" customWidth="1" style="8" min="6" max="6"/>
+    <col width="21.375" customWidth="1" style="8" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="4"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="4"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A3" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="H3"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B5" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>16</v>
+    <row r="1" ht="14.25" customHeight="1" s="8">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>表名</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>技能组表</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="8">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="16.5" customHeight="1" s="8">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>列作用说明</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>导出目标</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>需要导出的sheet</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>导出文件</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="n"/>
+      <c r="F3" s="0" t="n"/>
+      <c r="H3" s="0" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>生成文件</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>SpellGroup</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>combat/spell_group.py</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>SpellGroup</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>combat/spell_group.py</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="16.75" style="9" customWidth="1"/>
-    <col min="2" max="2" width="17" style="9" customWidth="1"/>
-    <col min="3" max="3" width="39" style="13" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="13"/>
+    <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
+    <col width="17" customWidth="1" style="9" min="2" max="2"/>
+    <col width="39" customWidth="1" style="13" min="3" max="3"/>
+    <col width="9" customWidth="1" style="13" min="4" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="10" t="s">
+    <row r="1" ht="64.5" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>技能列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36.75" customFormat="1" customHeight="1" s="15">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>group_id:int</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>name:string</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>spell_ids:list[int]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16.5" customFormat="1" customHeight="1" s="1">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customFormat="1" customHeight="1" s="1">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="8">
+      <c r="A5" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>102,103,104,105,106,107,108,109,110</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="8">
+      <c r="A6" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>201,202,203,204,205,206,207,208,209</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="8">
+      <c r="A7" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>301,303,303,304,305,306,307,308,309</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="8">
+      <c r="A8" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>401,404,403,404,405,406,407,408,409</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="8">
+      <c r="A9" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>501,505,503,504,505,506,507,508,509</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="8">
+      <c r="A10" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>601,606,603,604,605,606,607,608,609</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="8">
+      <c r="A11" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>701,707,703,704,705,706,707,708,709</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" s="8">
+      <c r="A12" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>801,808,803,804,805,806,807,808,809</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" s="8">
+      <c r="A13" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>刷兽潮前锋</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>9020,9021</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="15" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>刷兽潮首领</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>9022,9023</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-    </row>
-    <row r="4" spans="1:3" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-    </row>
-    <row r="5" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A5" s="16">
-        <v>1</v>
-      </c>
-      <c r="B5" s="11">
-        <v>1</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A6" s="16">
-        <v>2</v>
-      </c>
-      <c r="B6" s="11">
-        <v>2</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A7" s="16">
-        <v>3</v>
-      </c>
-      <c r="B7" s="11">
-        <v>3</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A8" s="16">
-        <v>4</v>
-      </c>
-      <c r="B8" s="11">
-        <v>4</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A9" s="16">
-        <v>5</v>
-      </c>
-      <c r="B9" s="11">
-        <v>5</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A10" s="16">
-        <v>6</v>
-      </c>
-      <c r="B10" s="11">
-        <v>6</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A11" s="16">
-        <v>7</v>
-      </c>
-      <c r="B11" s="11">
-        <v>7</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A12" s="16">
-        <v>8</v>
-      </c>
-      <c r="B12" s="11">
-        <v>8</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A13" s="16"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>兽王技能组</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>9024,9025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="A5:A13">
-    <cfRule type="duplicateValues" dxfId="2" priority="44"/>
+    <cfRule type="duplicateValues" priority="44" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A14:A1048576 A1:A4">
-    <cfRule type="duplicateValues" dxfId="1" priority="2039"/>
+  <conditionalFormatting sqref="A1:A4 A14:A1048576">
+    <cfRule type="duplicateValues" priority="2039" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="duplicateValues" dxfId="0" priority="2048"/>
+    <cfRule type="duplicateValues" priority="2048" dxfId="0"/>
   </conditionalFormatting>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/resources/combat/spell_group.xlsx
+++ b/resources/combat/spell_group.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\重要文档\RoundCA\data_table\normal\combat\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpellGroup" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CONFIG" sheetId="1" r:id="rId1"/>
+    <sheet name="SpellGroup" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">SpellGroup!#REF!</definedName>
@@ -233,86 +239,184 @@
     <definedName name="Z_FAF1ADB8_46A9_40B0_AA1B_9C75E39038F2_.wvu.FilterData" localSheetId="1" hidden="1">SpellGroup!$A$1:$B$4</definedName>
     <definedName name="Z_FF6A625A_6008_4A1D_8FF0_F8A30B9F02A0_.wvu.FilterData" localSheetId="1" hidden="1">SpellGroup!$A$1:$B$4</definedName>
   </definedNames>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+  <si>
+    <t>表名</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>生成文件</t>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>列作用说明</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>导出目标</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要导出的sheet</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>导出文件</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SERVER</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLIENT</t>
+  </si>
+  <si>
+    <t>名称</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>name:string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能列表</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>spell_ids:list[int]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>group_id:int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpellGroup</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>combat/spell_group.py</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能组表</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>102,103,104,105,106,107,108,109,110</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>201,202,203,204,205,206,207,208,209</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>301,303,303,304,305,306,307,308,309</t>
+  </si>
+  <si>
+    <t>401,404,403,404,405,406,407,408,409</t>
+  </si>
+  <si>
+    <t>501,505,503,504,505,506,507,508,509</t>
+  </si>
+  <si>
+    <t>601,606,603,604,605,606,607,608,609</t>
+  </si>
+  <si>
+    <t>701,707,703,704,705,706,707,708,709</t>
+  </si>
+  <si>
+    <t>801,808,803,804,805,806,807,808,809</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color indexed="8"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <color indexed="8"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -348,105 +452,102 @@
     </border>
   </borders>
   <cellStyleXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="9"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="9"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="9" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1"/>
+    <cellStyle name="常规 11" xfId="11"/>
+    <cellStyle name="常规 2" xfId="4"/>
     <cellStyle name="常规 2 2" xfId="2"/>
     <cellStyle name="常规 2 3" xfId="3"/>
-    <cellStyle name="常规 2" xfId="4"/>
     <cellStyle name="常规 3" xfId="5"/>
     <cellStyle name="常规 4" xfId="6"/>
     <cellStyle name="常规 5" xfId="7"/>
+    <cellStyle name="常规 6" xfId="1"/>
+    <cellStyle name="常规 7" xfId="10"/>
     <cellStyle name="常规_CONFIG" xfId="8"/>
     <cellStyle name="常规_Sheet1" xfId="9"/>
-    <cellStyle name="常规 7" xfId="10"/>
-    <cellStyle name="常规 11" xfId="11"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -481,74 +582,14 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -809,339 +850,235 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="21.125" customWidth="1" style="8" min="1" max="1"/>
-    <col width="65" customWidth="1" style="8" min="2" max="2"/>
-    <col width="49.5" customWidth="1" style="8" min="3" max="3"/>
-    <col width="30.125" customWidth="1" style="8" min="4" max="4"/>
-    <col width="23.5" customWidth="1" style="8" min="5" max="5"/>
-    <col width="19.25" customWidth="1" style="8" min="6" max="6"/>
-    <col width="21.375" customWidth="1" style="8" min="8" max="8"/>
+    <col min="1" max="1" width="21.125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="65" style="8" customWidth="1"/>
+    <col min="3" max="3" width="49.5" style="8" customWidth="1"/>
+    <col min="4" max="4" width="30.125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="23.5" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.25" style="8" customWidth="1"/>
+    <col min="8" max="8" width="21.375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="8">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>表名</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>技能组表</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" s="8">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="16.5" customHeight="1" s="8">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>列作用说明</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>导出目标</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>需要导出的sheet</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>导出文件</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="n"/>
-      <c r="F3" s="0" t="n"/>
-      <c r="H3" s="0" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>生成文件</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>SpellGroup</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>combat/spell_group.py</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>CLIENT</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>SpellGroup</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>combat/spell_group.py</t>
-        </is>
+    <row r="1" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="4"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="H3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="B5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
-    <col width="17" customWidth="1" style="9" min="2" max="2"/>
-    <col width="39" customWidth="1" style="13" min="3" max="3"/>
-    <col width="9" customWidth="1" style="13" min="4" max="16384"/>
+    <col min="1" max="1" width="16.75" style="9" customWidth="1"/>
+    <col min="2" max="2" width="17" style="9" customWidth="1"/>
+    <col min="3" max="3" width="39" style="13" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="64.5" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>技能列表</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36.75" customFormat="1" customHeight="1" s="15">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>group_id:int</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>name:string</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>spell_ids:list[int]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-    </row>
-    <row r="4" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" s="8">
-      <c r="A5" s="16" t="n">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="15" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+    </row>
+    <row r="4" spans="1:3" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A5" s="16">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>102,103,104,105,106,107,108,109,110</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1" s="8">
-      <c r="A6" s="16" t="n">
+      <c r="C5" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A6" s="16">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="11">
         <v>2</v>
       </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>201,202,203,204,205,206,207,208,209</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" s="8">
-      <c r="A7" s="16" t="n">
+      <c r="C6" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A7" s="16">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="11">
         <v>3</v>
       </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>301,303,303,304,305,306,307,308,309</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1" s="8">
-      <c r="A8" s="16" t="n">
+      <c r="C7" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A8" s="16">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="11">
         <v>4</v>
       </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>401,404,403,404,405,406,407,408,409</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1" s="8">
-      <c r="A9" s="16" t="n">
+      <c r="C8" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A9" s="16">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="11">
         <v>5</v>
       </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>501,505,503,504,505,506,507,508,509</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="8">
-      <c r="A10" s="16" t="n">
+      <c r="C9" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A10" s="16">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="11">
         <v>6</v>
       </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>601,606,603,604,605,606,607,608,609</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" s="8">
-      <c r="A11" s="16" t="n">
+      <c r="C10" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A11" s="16">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="11">
         <v>7</v>
       </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>701,707,703,704,705,706,707,708,709</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16.5" customHeight="1" s="8">
-      <c r="A12" s="16" t="n">
+      <c r="C11" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A12" s="16">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="11">
         <v>8</v>
       </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>801,808,803,804,805,806,807,808,809</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1" s="8">
-      <c r="A13" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>刷兽潮前锋</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>9020,9021</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>刷兽潮首领</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>9022,9023</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>兽王技能组</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>9024,9025</t>
-        </is>
-      </c>
+      <c r="C12" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A13" s="16"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="A5:A13">
-    <cfRule type="duplicateValues" priority="44" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A4 A14:A1048576">
-    <cfRule type="duplicateValues" priority="2039" dxfId="0"/>
+  <conditionalFormatting sqref="A14:A1048576 A1:A4">
+    <cfRule type="duplicateValues" dxfId="1" priority="2039"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="duplicateValues" priority="2048" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2048"/>
   </conditionalFormatting>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>